--- a/Plantilla_Rocita_Demo.xlsx
+++ b/Plantilla_Rocita_Demo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,16 @@
           <t>email</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tipo_documento</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sexo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -459,6 +469,16 @@
           <t>juan@mail.com</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -477,6 +497,16 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>maria@mail.com</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -491,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +540,16 @@
           <t>especialidad</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>correo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>celular</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -525,6 +565,16 @@
           <t>Diagnostico</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>house@mail.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5550101</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -538,6 +588,16 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Cirugia</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>doctor3@mail.com</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5550203</t>
         </is>
       </c>
     </row>
